--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/79.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/79.xlsx
@@ -426,13 +426,13 @@
         <v>-11.938765768108</v>
       </c>
       <c r="E2">
-        <v>-8.535926515095804</v>
+        <v>-7.574853004921931</v>
       </c>
       <c r="F2">
-        <v>2.260072017217124</v>
+        <v>1.515278880774684</v>
       </c>
       <c r="G2">
-        <v>-13.88311154524706</v>
+        <v>-13.15825766778702</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.28989019158775</v>
       </c>
       <c r="E3">
-        <v>-8.287462731716955</v>
+        <v>-6.370998946248836</v>
       </c>
       <c r="F3">
-        <v>2.053982782735073</v>
+        <v>1.753799244993103</v>
       </c>
       <c r="G3">
-        <v>-13.5504348240057</v>
+        <v>-12.27343822986939</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-10.59637078469771</v>
       </c>
       <c r="E4">
-        <v>-9.444170847496194</v>
+        <v>-8.610646336222365</v>
       </c>
       <c r="F4">
-        <v>2.4042494363469</v>
+        <v>2.248990826926794</v>
       </c>
       <c r="G4">
-        <v>-12.44295471420777</v>
+        <v>-11.28587601114048</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.935898004072254</v>
       </c>
       <c r="E5">
-        <v>-10.91157303646769</v>
+        <v>-9.392903993255358</v>
       </c>
       <c r="F5">
-        <v>2.251695796630365</v>
+        <v>2.30157461443713</v>
       </c>
       <c r="G5">
-        <v>-12.40973670026673</v>
+        <v>-12.1468628317209</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.312292592329849</v>
       </c>
       <c r="E6">
-        <v>-11.08061191422601</v>
+        <v>-11.02753819885611</v>
       </c>
       <c r="F6">
-        <v>2.610178716531492</v>
+        <v>1.969905419390308</v>
       </c>
       <c r="G6">
-        <v>-11.05763375948097</v>
+        <v>-10.9204215785148</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.726657179022775</v>
       </c>
       <c r="E7">
-        <v>-11.35711600866035</v>
+        <v>-10.28875842077076</v>
       </c>
       <c r="F7">
-        <v>3.110161008859387</v>
+        <v>2.342367711407019</v>
       </c>
       <c r="G7">
-        <v>-11.07162412492993</v>
+        <v>-10.12102083660144</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.175887691308546</v>
       </c>
       <c r="E8">
-        <v>-11.75716593097196</v>
+        <v>-11.23602914216925</v>
       </c>
       <c r="F8">
-        <v>2.848634148807379</v>
+        <v>2.928367406826093</v>
       </c>
       <c r="G8">
-        <v>-10.00037793605932</v>
+        <v>-10.16504778172821</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.652167585358698</v>
       </c>
       <c r="E9">
-        <v>-12.62294223412842</v>
+        <v>-12.08933855638259</v>
       </c>
       <c r="F9">
-        <v>3.029048342988325</v>
+        <v>2.92873641030439</v>
       </c>
       <c r="G9">
-        <v>-10.3435855026611</v>
+        <v>-9.302164018553793</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.128266230515277</v>
       </c>
       <c r="E10">
-        <v>-14.08931645950017</v>
+        <v>-12.335180353311</v>
       </c>
       <c r="F10">
-        <v>3.153777853476505</v>
+        <v>3.326968764977132</v>
       </c>
       <c r="G10">
-        <v>-7.973354076182349</v>
+        <v>-7.879582873782493</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.598953870813751</v>
       </c>
       <c r="E11">
-        <v>-15.01238701580167</v>
+        <v>-13.78255763022058</v>
       </c>
       <c r="F11">
-        <v>3.532630398862014</v>
+        <v>3.131023166883471</v>
       </c>
       <c r="G11">
-        <v>-7.833447111147209</v>
+        <v>-6.764011790686585</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.049019406314967</v>
       </c>
       <c r="E12">
-        <v>-15.1894005362875</v>
+        <v>-15.0116352891164</v>
       </c>
       <c r="F12">
-        <v>3.90537934164942</v>
+        <v>3.868216098637717</v>
       </c>
       <c r="G12">
-        <v>-7.48282061199192</v>
+        <v>-7.65520402876731</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.462606659471912</v>
       </c>
       <c r="E13">
-        <v>-15.64636431992751</v>
+        <v>-14.06077801630383</v>
       </c>
       <c r="F13">
-        <v>3.934674733673218</v>
+        <v>3.583605141162264</v>
       </c>
       <c r="G13">
-        <v>-6.571275139935755</v>
+        <v>-6.970497137062007</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.845475516650679</v>
       </c>
       <c r="E14">
-        <v>-17.53954722052219</v>
+        <v>-16.65403582764031</v>
       </c>
       <c r="F14">
-        <v>3.905138618350273</v>
+        <v>4.220311932581877</v>
       </c>
       <c r="G14">
-        <v>-5.902866063920285</v>
+        <v>-5.781988114644876</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.194508779509431</v>
       </c>
       <c r="E15">
-        <v>-17.49343376970209</v>
+        <v>-16.2038013563757</v>
       </c>
       <c r="F15">
-        <v>4.282808135416949</v>
+        <v>4.342334889660571</v>
       </c>
       <c r="G15">
-        <v>-5.379796558169898</v>
+        <v>-5.626657317942271</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.513268896160521</v>
       </c>
       <c r="E16">
-        <v>-17.77117866601453</v>
+        <v>-16.95571370908329</v>
       </c>
       <c r="F16">
-        <v>4.420289645936247</v>
+        <v>3.852683111019088</v>
       </c>
       <c r="G16">
-        <v>-4.393611526385325</v>
+        <v>-4.773503248107772</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.818771432355497</v>
       </c>
       <c r="E17">
-        <v>-19.01286359654771</v>
+        <v>-19.47992134875081</v>
       </c>
       <c r="F17">
-        <v>4.441625332029047</v>
+        <v>4.157974100338349</v>
       </c>
       <c r="G17">
-        <v>-5.311768157883415</v>
+        <v>-4.42824976436272</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.123419979289392</v>
       </c>
       <c r="E18">
-        <v>-20.36139334281785</v>
+        <v>-19.3410556933056</v>
       </c>
       <c r="F18">
-        <v>4.450565351921703</v>
+        <v>4.38808023502804</v>
       </c>
       <c r="G18">
-        <v>-4.153325510053945</v>
+        <v>-4.231868202973153</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.450173797265032</v>
       </c>
       <c r="E19">
-        <v>-21.68722637736156</v>
+        <v>-19.50044892142758</v>
       </c>
       <c r="F19">
-        <v>4.414844864998966</v>
+        <v>4.236643107981889</v>
       </c>
       <c r="G19">
-        <v>-3.800123406469101</v>
+        <v>-3.836400364488435</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.8291269467083331</v>
       </c>
       <c r="E20">
-        <v>-21.58519532949474</v>
+        <v>-20.67873521585337</v>
       </c>
       <c r="F20">
-        <v>4.822223121333371</v>
+        <v>4.614089322514488</v>
       </c>
       <c r="G20">
-        <v>-3.494983803023398</v>
+        <v>-3.64028364674201</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.2842060656208668</v>
       </c>
       <c r="E21">
-        <v>-22.35162144139692</v>
+        <v>-19.40149270741197</v>
       </c>
       <c r="F21">
-        <v>4.715571613869932</v>
+        <v>4.935217370988145</v>
       </c>
       <c r="G21">
-        <v>-3.45259226739303</v>
+        <v>-2.93035701911854</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.1531237402977567</v>
       </c>
       <c r="E22">
-        <v>-24.0552333630825</v>
+        <v>-22.83225103020101</v>
       </c>
       <c r="F22">
-        <v>4.587616094432002</v>
+        <v>4.84355564001434</v>
       </c>
       <c r="G22">
-        <v>-2.664132878486968</v>
+        <v>-1.934584647452237</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.4578232721464157</v>
       </c>
       <c r="E23">
-        <v>-23.3189623595974</v>
+        <v>-22.59625866423928</v>
       </c>
       <c r="F23">
-        <v>4.713663248241827</v>
+        <v>4.448219883460937</v>
       </c>
       <c r="G23">
-        <v>-3.009839906970901</v>
+        <v>-2.687942322005407</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.6194179941214629</v>
       </c>
       <c r="E24">
-        <v>-24.08354538257846</v>
+        <v>-22.6312184835785</v>
       </c>
       <c r="F24">
-        <v>4.809672251953513</v>
+        <v>4.962241728729204</v>
       </c>
       <c r="G24">
-        <v>-1.976923214353977</v>
+        <v>-1.808141671125314</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.6259105880394876</v>
       </c>
       <c r="E25">
-        <v>-22.64088224711087</v>
+        <v>-22.81366617287353</v>
       </c>
       <c r="F25">
-        <v>4.601497276780829</v>
+        <v>4.850497023041711</v>
       </c>
       <c r="G25">
-        <v>-2.686353260146556</v>
+        <v>-3.779856246677683</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.4814638290659326</v>
       </c>
       <c r="E26">
-        <v>-23.61175084656333</v>
+        <v>-24.43927060130299</v>
       </c>
       <c r="F26">
-        <v>4.82238307563083</v>
+        <v>4.632644021019776</v>
       </c>
       <c r="G26">
-        <v>-2.158927076466489</v>
+        <v>-1.695113025323517</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.204408468708469</v>
       </c>
       <c r="E27">
-        <v>-23.79145880908372</v>
+        <v>-22.75822406559762</v>
       </c>
       <c r="F27">
-        <v>4.488170448883813</v>
+        <v>4.868769821894052</v>
       </c>
       <c r="G27">
-        <v>-1.399759394491899</v>
+        <v>-1.04762659711624</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.1896866977094298</v>
       </c>
       <c r="E28">
-        <v>-23.78950250831241</v>
+        <v>-23.5699937877386</v>
       </c>
       <c r="F28">
-        <v>4.602371482446151</v>
+        <v>4.208888661813813</v>
       </c>
       <c r="G28">
-        <v>-2.04204495565698</v>
+        <v>-1.773417358963898</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.6718564247254251</v>
       </c>
       <c r="E29">
-        <v>-23.12690071998409</v>
+        <v>-24.05903275277494</v>
       </c>
       <c r="F29">
-        <v>4.212936614133675</v>
+        <v>4.312966647164663</v>
       </c>
       <c r="G29">
-        <v>-2.063570122753322</v>
+        <v>-0.6506723236843893</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.212970316444424</v>
       </c>
       <c r="E30">
-        <v>-22.94991437034231</v>
+        <v>-22.11932883869946</v>
       </c>
       <c r="F30">
-        <v>4.724994664066797</v>
+        <v>4.443807678780523</v>
       </c>
       <c r="G30">
-        <v>-2.306405259149942</v>
+        <v>-0.6250023535728806</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.793566598023735</v>
       </c>
       <c r="E31">
-        <v>-22.89821278259673</v>
+        <v>-23.72340943017046</v>
       </c>
       <c r="F31">
-        <v>4.665127413051355</v>
+        <v>4.338556167346333</v>
       </c>
       <c r="G31">
-        <v>-1.868943150499568</v>
+        <v>-1.584742747589755</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.39112791185855</v>
       </c>
       <c r="E32">
-        <v>-22.84208687574567</v>
+        <v>-22.72725836033317</v>
       </c>
       <c r="F32">
-        <v>4.504222892042707</v>
+        <v>4.306307163790239</v>
       </c>
       <c r="G32">
-        <v>-2.891673294492155</v>
+        <v>-1.332184538944295</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.994985668341211</v>
       </c>
       <c r="E33">
-        <v>-22.46963800251081</v>
+        <v>-21.85784569254855</v>
       </c>
       <c r="F33">
-        <v>4.39557749883173</v>
+        <v>5.069811785623597</v>
       </c>
       <c r="G33">
-        <v>-3.311268388867082</v>
+        <v>-2.102363095382501</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.603539223134253</v>
       </c>
       <c r="E34">
-        <v>-23.05801357337941</v>
+        <v>-22.19590986264317</v>
       </c>
       <c r="F34">
-        <v>4.613674391564643</v>
+        <v>4.299829806596092</v>
       </c>
       <c r="G34">
-        <v>-3.377429641469417</v>
+        <v>-1.749746958358109</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.209254623663609</v>
       </c>
       <c r="E35">
-        <v>-21.71078802762347</v>
+        <v>-20.57914954395069</v>
       </c>
       <c r="F35">
-        <v>4.604998850559865</v>
+        <v>4.417125401517199</v>
       </c>
       <c r="G35">
-        <v>-2.874306172593139</v>
+        <v>-2.718968754799456</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.818020038788338</v>
       </c>
       <c r="E36">
-        <v>-21.34065773308054</v>
+        <v>-20.07194234119558</v>
       </c>
       <c r="F36">
-        <v>4.597601360228848</v>
+        <v>4.477524777720228</v>
       </c>
       <c r="G36">
-        <v>-3.742490119175929</v>
+        <v>-3.40498662253831</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.433405782832933</v>
       </c>
       <c r="E37">
-        <v>-20.46928876452461</v>
+        <v>-20.2003608071051</v>
       </c>
       <c r="F37">
-        <v>4.613815341391117</v>
+        <v>4.806438324474186</v>
       </c>
       <c r="G37">
-        <v>-3.839720841664324</v>
+        <v>-2.748770285743976</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.046625227926968</v>
       </c>
       <c r="E38">
-        <v>-19.19472711269575</v>
+        <v>-19.70817908110743</v>
       </c>
       <c r="F38">
-        <v>4.526279164327033</v>
+        <v>4.467453991803949</v>
       </c>
       <c r="G38">
-        <v>-4.259190135308758</v>
+        <v>-2.945694776601983</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.660681671008599</v>
       </c>
       <c r="E39">
-        <v>-18.03392978488758</v>
+        <v>-19.39134439716078</v>
       </c>
       <c r="F39">
-        <v>4.484839915343644</v>
+        <v>4.789072989111393</v>
       </c>
       <c r="G39">
-        <v>-4.577532194365076</v>
+        <v>-3.025985437565927</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.268680004651909</v>
       </c>
       <c r="E40">
-        <v>-17.53678032290351</v>
+        <v>-19.46327014982461</v>
       </c>
       <c r="F40">
-        <v>4.601757004550961</v>
+        <v>4.567799182312108</v>
       </c>
       <c r="G40">
-        <v>-4.072942153814901</v>
+        <v>-3.02342638586407</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.855374373961514</v>
       </c>
       <c r="E41">
-        <v>-17.09949275882683</v>
+        <v>-18.01420375211017</v>
       </c>
       <c r="F41">
-        <v>5.155358828057889</v>
+        <v>4.729161394330318</v>
       </c>
       <c r="G41">
-        <v>-4.920474917323717</v>
+        <v>-4.254578545372554</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.421241955708036</v>
       </c>
       <c r="E42">
-        <v>-17.56142880692726</v>
+        <v>-16.10316055002923</v>
       </c>
       <c r="F42">
-        <v>5.296213632177074</v>
+        <v>4.77160312915818</v>
       </c>
       <c r="G42">
-        <v>-4.747157926706253</v>
+        <v>-3.547446018184228</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.956633332409464</v>
       </c>
       <c r="E43">
-        <v>-16.2250534848937</v>
+        <v>-17.13198908830587</v>
       </c>
       <c r="F43">
-        <v>4.942432735138887</v>
+        <v>4.508641431546783</v>
       </c>
       <c r="G43">
-        <v>-4.471770196021978</v>
+        <v>-4.869307125468741</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.452971405160211</v>
       </c>
       <c r="E44">
-        <v>-14.72778600984161</v>
+        <v>-15.43297356773807</v>
       </c>
       <c r="F44">
-        <v>4.958371151471869</v>
+        <v>4.527921467361343</v>
       </c>
       <c r="G44">
-        <v>-4.836267880986815</v>
+        <v>-3.466231715014827</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.917428852353344</v>
       </c>
       <c r="E45">
-        <v>-15.04323498074192</v>
+        <v>-15.68269626689105</v>
       </c>
       <c r="F45">
-        <v>5.143387595043083</v>
+        <v>4.96452068154152</v>
       </c>
       <c r="G45">
-        <v>-5.589897020274204</v>
+        <v>-3.508103494995529</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.34258536613341</v>
       </c>
       <c r="E46">
-        <v>-14.25107355105416</v>
+        <v>-13.86387996645032</v>
       </c>
       <c r="F46">
-        <v>5.097441119024354</v>
+        <v>4.500952539327325</v>
       </c>
       <c r="G46">
-        <v>-5.766690083707903</v>
+        <v>-4.811812881088219</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.73050491461065</v>
       </c>
       <c r="E47">
-        <v>-14.38083697374395</v>
+        <v>-13.45286660856615</v>
       </c>
       <c r="F47">
-        <v>5.510132708705058</v>
+        <v>4.602190939971791</v>
       </c>
       <c r="G47">
-        <v>-5.43784035310994</v>
+        <v>-5.207535631579461</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-11.09061221820452</v>
       </c>
       <c r="E48">
-        <v>-12.90518843360449</v>
+        <v>-12.22118960558993</v>
       </c>
       <c r="F48">
-        <v>5.454071103004416</v>
+        <v>5.029495384134255</v>
       </c>
       <c r="G48">
-        <v>-5.78396451033182</v>
+        <v>-6.138381584129577</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-11.4110667079694</v>
       </c>
       <c r="E49">
-        <v>-12.56248257765201</v>
+        <v>-11.98379794115983</v>
       </c>
       <c r="F49">
-        <v>5.001194559425352</v>
+        <v>4.891396228307936</v>
       </c>
       <c r="G49">
-        <v>-6.16498181753762</v>
+        <v>-5.40895253273426</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-11.69838551215962</v>
       </c>
       <c r="E50">
-        <v>-12.09274849731037</v>
+        <v>-12.2518745454659</v>
       </c>
       <c r="F50">
-        <v>5.483255635614134</v>
+        <v>5.207657548503446</v>
       </c>
       <c r="G50">
-        <v>-6.106275913489724</v>
+        <v>-6.05028796732957</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-11.95566344961002</v>
       </c>
       <c r="E51">
-        <v>-12.39204440142532</v>
+        <v>-12.96560733381482</v>
       </c>
       <c r="F51">
-        <v>5.51286143399736</v>
+        <v>4.759671488791259</v>
       </c>
       <c r="G51">
-        <v>-6.2150372660914</v>
+        <v>-5.075474659472394</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-12.16650317927514</v>
       </c>
       <c r="E52">
-        <v>-11.02480300055548</v>
+        <v>-12.55251087788712</v>
       </c>
       <c r="F52">
-        <v>5.384701616496338</v>
+        <v>5.084720793111544</v>
       </c>
       <c r="G52">
-        <v>-6.101098220266304</v>
+        <v>-5.908288737513611</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-12.34162462881462</v>
       </c>
       <c r="E53">
-        <v>-11.61135812487299</v>
+        <v>-11.3595025144624</v>
       </c>
       <c r="F53">
-        <v>5.441816386630746</v>
+        <v>5.155051589110294</v>
       </c>
       <c r="G53">
-        <v>-5.550680297815998</v>
+        <v>-4.617775185940456</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-12.47948460710091</v>
       </c>
       <c r="E54">
-        <v>-9.840104386934829</v>
+        <v>-11.52811571566399</v>
       </c>
       <c r="F54">
-        <v>5.434463240065361</v>
+        <v>5.504588154295104</v>
       </c>
       <c r="G54">
-        <v>-6.618430550597134</v>
+        <v>-6.75903273019552</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-12.56607742998207</v>
       </c>
       <c r="E55">
-        <v>-10.52648972075143</v>
+        <v>-9.78608422049733</v>
       </c>
       <c r="F55">
-        <v>5.233581230633275</v>
+        <v>5.257743831785135</v>
       </c>
       <c r="G55">
-        <v>-6.126877438380609</v>
+        <v>-5.640770173576185</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.61617625360337</v>
       </c>
       <c r="E56">
-        <v>-9.638211430250861</v>
+        <v>-10.20150831206498</v>
       </c>
       <c r="F56">
-        <v>5.301124704220852</v>
+        <v>4.858649941094393</v>
       </c>
       <c r="G56">
-        <v>-6.699154893026723</v>
+        <v>-5.805784315981157</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-12.62547606798606</v>
       </c>
       <c r="E57">
-        <v>-8.995779465152706</v>
+        <v>-9.156232356192481</v>
       </c>
       <c r="F57">
-        <v>5.717864246221419</v>
+        <v>5.190418909613888</v>
       </c>
       <c r="G57">
-        <v>-6.780594313292794</v>
+        <v>-5.62907401618594</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.586723304085</v>
       </c>
       <c r="E58">
-        <v>-8.77506617049286</v>
+        <v>-9.344716501339738</v>
       </c>
       <c r="F58">
-        <v>5.31440091090998</v>
+        <v>5.007065357253886</v>
       </c>
       <c r="G58">
-        <v>-7.14418490877987</v>
+        <v>-6.134200365113477</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.51462274428403</v>
       </c>
       <c r="E59">
-        <v>-9.751482150604719</v>
+        <v>-8.638016433124724</v>
       </c>
       <c r="F59">
-        <v>5.442682673766491</v>
+        <v>5.297749826915051</v>
       </c>
       <c r="G59">
-        <v>-6.987486856769547</v>
+        <v>-6.289809247641379</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-12.40104047813359</v>
       </c>
       <c r="E60">
-        <v>-9.033682792596906</v>
+        <v>-7.315502770028642</v>
       </c>
       <c r="F60">
-        <v>5.055986032981811</v>
+        <v>5.1267618503428</v>
       </c>
       <c r="G60">
-        <v>-7.285138006205419</v>
+        <v>-6.262143018569691</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-12.24777994164309</v>
       </c>
       <c r="E61">
-        <v>-7.891479379064235</v>
+        <v>-9.052774839013244</v>
       </c>
       <c r="F61">
-        <v>5.252096336490677</v>
+        <v>4.947179101767459</v>
       </c>
       <c r="G61">
-        <v>-7.251072492606318</v>
+        <v>-7.155881066170115</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-12.06806585205318</v>
       </c>
       <c r="E62">
-        <v>-7.237925481803241</v>
+        <v>-8.286570622337443</v>
       </c>
       <c r="F62">
-        <v>5.34746393930661</v>
+        <v>4.841355872497795</v>
       </c>
       <c r="G62">
-        <v>-7.448718682391887</v>
+        <v>-6.208393001194083</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.85249132775804</v>
       </c>
       <c r="E63">
-        <v>-8.003676851078277</v>
+        <v>-8.68244076313997</v>
       </c>
       <c r="F63">
-        <v>4.971153241915381</v>
+        <v>4.76270270191341</v>
       </c>
       <c r="G63">
-        <v>-7.411875621085338</v>
+        <v>-6.409326562700148</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.61216989358647</v>
       </c>
       <c r="E64">
-        <v>-7.649763021956814</v>
+        <v>-5.720320629982713</v>
       </c>
       <c r="F64">
-        <v>5.093201538288723</v>
+        <v>5.086225313731211</v>
       </c>
       <c r="G64">
-        <v>-7.356801385494022</v>
+        <v>-7.414328735329938</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.35744813099648</v>
       </c>
       <c r="E65">
-        <v>-6.267324062317231</v>
+        <v>-8.097171725440639</v>
       </c>
       <c r="F65">
-        <v>5.114903060447989</v>
+        <v>4.7826320571533</v>
       </c>
       <c r="G65">
-        <v>-7.807720861761533</v>
+        <v>-7.179942111149538</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.07844510990893</v>
       </c>
       <c r="E66">
-        <v>-7.946704119587776</v>
+        <v>-8.051225828158815</v>
       </c>
       <c r="F66">
-        <v>4.932805386878931</v>
+        <v>4.318017085328998</v>
       </c>
       <c r="G66">
-        <v>-8.14986243269967</v>
+        <v>-7.060779024463471</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.79271294835677</v>
       </c>
       <c r="E67">
-        <v>-7.825929717803207</v>
+        <v>-7.987546426662954</v>
       </c>
       <c r="F67">
-        <v>5.006205404941802</v>
+        <v>4.903133072847257</v>
       </c>
       <c r="G67">
-        <v>-8.177839853052051</v>
+        <v>-6.108583363730596</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.50583175112027</v>
       </c>
       <c r="E68">
-        <v>-6.492180910694095</v>
+        <v>-7.673659779295291</v>
       </c>
       <c r="F68">
-        <v>4.640496034948526</v>
+        <v>4.565105298549946</v>
       </c>
       <c r="G68">
-        <v>-7.844964499078334</v>
+        <v>-7.631977241263783</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.20969222614912</v>
       </c>
       <c r="E69">
-        <v>-7.247738684977863</v>
+        <v>-7.066903132429563</v>
       </c>
       <c r="F69">
-        <v>4.798804861961768</v>
+        <v>4.333678353126779</v>
       </c>
       <c r="G69">
-        <v>-8.056720233952277</v>
+        <v>-7.2479771325271</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.923480232908979</v>
       </c>
       <c r="E70">
-        <v>-7.44269401948208</v>
+        <v>-8.282626321476762</v>
       </c>
       <c r="F70">
-        <v>4.782679568330764</v>
+        <v>4.377748137635713</v>
       </c>
       <c r="G70">
-        <v>-8.469495604516304</v>
+        <v>-6.579455497963294</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.646519488808806</v>
       </c>
       <c r="E71">
-        <v>-7.459340689934276</v>
+        <v>-6.923803353787179</v>
       </c>
       <c r="F71">
-        <v>4.835659282319959</v>
+        <v>4.396705097443523</v>
       </c>
       <c r="G71">
-        <v>-8.034317772288029</v>
+        <v>-7.704014712198324</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.372513998340725</v>
       </c>
       <c r="E72">
-        <v>-8.076259232473216</v>
+        <v>-8.75819307634028</v>
       </c>
       <c r="F72">
-        <v>4.678587329626675</v>
+        <v>3.898228909441211</v>
       </c>
       <c r="G72">
-        <v>-7.609031850131094</v>
+        <v>-6.766752922393101</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.115737038564435</v>
       </c>
       <c r="E73">
-        <v>-7.729296610953529</v>
+        <v>-7.781636713534184</v>
       </c>
       <c r="F73">
-        <v>4.328841715261027</v>
+        <v>4.302214867704744</v>
       </c>
       <c r="G73">
-        <v>-7.311129099234237</v>
+        <v>-6.319756442589627</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.868220998702375</v>
       </c>
       <c r="E74">
-        <v>-7.236920160573539</v>
+        <v>-8.744544255681163</v>
       </c>
       <c r="F74">
-        <v>4.417743046824221</v>
+        <v>3.887947490638178</v>
       </c>
       <c r="G74">
-        <v>-8.09445383200889</v>
+        <v>-7.323874699560431</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.627136651267879</v>
       </c>
       <c r="E75">
-        <v>-8.189951100909788</v>
+        <v>-7.359601049915336</v>
       </c>
       <c r="F75">
-        <v>4.393021397484211</v>
+        <v>4.024816106968201</v>
       </c>
       <c r="G75">
-        <v>-7.065539588948943</v>
+        <v>-5.841445512530187</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.398318903391408</v>
       </c>
       <c r="E76">
-        <v>-9.131674441648885</v>
+        <v>-9.412303975904218</v>
       </c>
       <c r="F76">
-        <v>4.174897581750736</v>
+        <v>3.571600650323233</v>
       </c>
       <c r="G76">
-        <v>-7.131280402267791</v>
+        <v>-6.692464280491856</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.167876969255721</v>
       </c>
       <c r="E77">
-        <v>-9.625975493482136</v>
+        <v>-8.59280867710615</v>
       </c>
       <c r="F77">
-        <v>4.39009787636431</v>
+        <v>4.302013737053483</v>
       </c>
       <c r="G77">
-        <v>-6.788536312041505</v>
+        <v>-6.201987095575594</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.935408520182071</v>
       </c>
       <c r="E78">
-        <v>-9.261469563656734</v>
+        <v>-9.853114692758865</v>
       </c>
       <c r="F78">
-        <v>4.339783539430798</v>
+        <v>4.097254815540402</v>
       </c>
       <c r="G78">
-        <v>-6.274723091618921</v>
+        <v>-5.954924392525324</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.700761759756636</v>
       </c>
       <c r="E79">
-        <v>-9.268334730252361</v>
+        <v>-8.963545787166108</v>
       </c>
       <c r="F79">
-        <v>4.201605198308706</v>
+        <v>3.823238850639237</v>
       </c>
       <c r="G79">
-        <v>-6.795021670752938</v>
+        <v>-6.077328503294337</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.449624474838969</v>
       </c>
       <c r="E80">
-        <v>-10.58439984636152</v>
+        <v>-11.20767183793322</v>
       </c>
       <c r="F80">
-        <v>3.630286456725757</v>
+        <v>3.673041765324875</v>
       </c>
       <c r="G80">
-        <v>-6.311615811108559</v>
+        <v>-6.338692763074258</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.186353774388703</v>
       </c>
       <c r="E81">
-        <v>-12.0748791388761</v>
+        <v>-11.61388048489526</v>
       </c>
       <c r="F81">
-        <v>4.008077919147921</v>
+        <v>3.737375067021857</v>
       </c>
       <c r="G81">
-        <v>-6.362813397873388</v>
+        <v>-5.050973311936248</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.908823624645616</v>
       </c>
       <c r="E82">
-        <v>-11.87141480171148</v>
+        <v>-12.24407651322469</v>
       </c>
       <c r="F82">
-        <v>4.053017158204431</v>
+        <v>3.761467985113437</v>
       </c>
       <c r="G82">
-        <v>-6.121577254972236</v>
+        <v>-5.086651061212973</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.606987689246798</v>
       </c>
       <c r="E83">
-        <v>-13.30580441516705</v>
+        <v>-13.65807440822373</v>
       </c>
       <c r="F83">
-        <v>3.81051060619685</v>
+        <v>3.345767354193399</v>
       </c>
       <c r="G83">
-        <v>-4.935402167160291</v>
+        <v>-4.661831925977077</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.288804321096531</v>
       </c>
       <c r="E84">
-        <v>-14.31851611445039</v>
+        <v>-14.16848777057627</v>
       </c>
       <c r="F84">
-        <v>4.082208025637811</v>
+        <v>3.679756678406339</v>
       </c>
       <c r="G84">
-        <v>-4.530469478978796</v>
+        <v>-4.895235318132314</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.952228656738313</v>
       </c>
       <c r="E85">
-        <v>-14.66700936018467</v>
+        <v>-15.75089961392057</v>
       </c>
       <c r="F85">
-        <v>3.707322663570478</v>
+        <v>3.696743508055342</v>
       </c>
       <c r="G85">
-        <v>-4.606148550006536</v>
+        <v>-4.445858556086104</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.593217429105502</v>
       </c>
       <c r="E86">
-        <v>-17.01746398065189</v>
+        <v>-17.72577618561363</v>
       </c>
       <c r="F86">
-        <v>3.900919625791542</v>
+        <v>3.072020619297859</v>
       </c>
       <c r="G86">
-        <v>-4.16465419688933</v>
+        <v>-3.629726317017274</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.223470883499514</v>
       </c>
       <c r="E87">
-        <v>-17.17455674397797</v>
+        <v>-19.77277323435284</v>
       </c>
       <c r="F87">
-        <v>3.468862480176845</v>
+        <v>3.547107054635046</v>
       </c>
       <c r="G87">
-        <v>-4.21380586651089</v>
+        <v>-4.380491834413194</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.844304939665318</v>
       </c>
       <c r="E88">
-        <v>-20.33811698641843</v>
+        <v>-20.85602950172767</v>
       </c>
       <c r="F88">
-        <v>3.366255757621438</v>
+        <v>2.737012972181291</v>
       </c>
       <c r="G88">
-        <v>-3.475335715247823</v>
+        <v>-2.564790027944519</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.46101908328869</v>
       </c>
       <c r="E89">
-        <v>-20.47354100161781</v>
+        <v>-21.74858720016549</v>
       </c>
       <c r="F89">
-        <v>3.373315918592468</v>
+        <v>2.898324505610207</v>
       </c>
       <c r="G89">
-        <v>-2.96224088320726</v>
+        <v>-3.407446357873988</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.084867345612283</v>
       </c>
       <c r="E90">
-        <v>-21.8637779934986</v>
+        <v>-22.29776430002369</v>
       </c>
       <c r="F90">
-        <v>2.929574190733658</v>
+        <v>3.090659254216666</v>
       </c>
       <c r="G90">
-        <v>-3.184481115804074</v>
+        <v>-3.385149833666997</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.716294248370689</v>
       </c>
       <c r="E91">
-        <v>-24.46502403298461</v>
+        <v>-25.32731341115516</v>
       </c>
       <c r="F91">
-        <v>3.167693877355471</v>
+        <v>3.066301857237207</v>
       </c>
       <c r="G91">
-        <v>-3.203331362104684</v>
+        <v>-2.519164089322283</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.36020575974797</v>
       </c>
       <c r="E92">
-        <v>-26.241136823533</v>
+        <v>-28.50305977715026</v>
       </c>
       <c r="F92">
-        <v>2.975137409920851</v>
+        <v>2.006837441338357</v>
       </c>
       <c r="G92">
-        <v>-2.753057442217332</v>
+        <v>-2.725338244417014</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.020527778387994</v>
       </c>
       <c r="E93">
-        <v>-28.05513482762956</v>
+        <v>-29.08552116096483</v>
       </c>
       <c r="F93">
-        <v>2.780126198317299</v>
+        <v>2.498841023264268</v>
       </c>
       <c r="G93">
-        <v>-2.313506379331678</v>
+        <v>-2.20261965649379</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.693207948478846</v>
       </c>
       <c r="E94">
-        <v>-30.03853851587906</v>
+        <v>-31.07291217057809</v>
       </c>
       <c r="F94">
-        <v>2.247182234771362</v>
+        <v>2.450050211421409</v>
       </c>
       <c r="G94">
-        <v>-2.904177224993983</v>
+        <v>-2.396253465085762</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.380973691281486</v>
       </c>
       <c r="E95">
-        <v>-32.59377073097313</v>
+        <v>-31.83945828704147</v>
       </c>
       <c r="F95">
-        <v>2.057169199036938</v>
+        <v>2.313330463447437</v>
       </c>
       <c r="G95">
-        <v>-2.621493051941155</v>
+        <v>-1.959850731007955</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.079369314345763</v>
       </c>
       <c r="E96">
-        <v>-34.32384252628554</v>
+        <v>-34.99034333073446</v>
       </c>
       <c r="F96">
-        <v>1.913333860384896</v>
+        <v>2.034812022628679</v>
       </c>
       <c r="G96">
-        <v>-2.763932584313837</v>
+        <v>-1.191254615337521</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.783775892122925</v>
       </c>
       <c r="E97">
-        <v>-36.06916622205578</v>
+        <v>-37.61172522989557</v>
       </c>
       <c r="F97">
-        <v>1.472392124584583</v>
+        <v>2.259786950152345</v>
       </c>
       <c r="G97">
-        <v>-3.055839937239075</v>
+        <v>-3.303816350858183</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.48589153453998</v>
       </c>
       <c r="E98">
-        <v>-39.09971386170594</v>
+        <v>-38.85809713102668</v>
       </c>
       <c r="F98">
-        <v>1.277011909502734</v>
+        <v>1.72070295877225</v>
       </c>
       <c r="G98">
-        <v>-2.71204640407684</v>
+        <v>-2.321375546078526</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.187097622488319</v>
       </c>
       <c r="E99">
-        <v>-41.08477723567925</v>
+        <v>-42.08450127150859</v>
       </c>
       <c r="F99">
-        <v>0.7979677930828638</v>
+        <v>1.352798572380173</v>
       </c>
       <c r="G99">
-        <v>-3.165716943687485</v>
+        <v>-2.447206071480684</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.8628488919574367</v>
       </c>
       <c r="E100">
-        <v>-44.30748161289689</v>
+        <v>-43.67640932484697</v>
       </c>
       <c r="F100">
-        <v>0.6112552004762146</v>
+        <v>0.6116321224840893</v>
       </c>
       <c r="G100">
-        <v>-2.848073409739954</v>
+        <v>-2.748836496654761</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.5320723164320097</v>
       </c>
       <c r="E101">
-        <v>-46.23211250123784</v>
+        <v>-46.98346332316848</v>
       </c>
       <c r="F101">
-        <v>0.3148361316952442</v>
+        <v>0.3989111194811358</v>
       </c>
       <c r="G101">
-        <v>-2.745131996196316</v>
+        <v>-2.624363294923703</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.1494448049736538</v>
       </c>
       <c r="E102">
-        <v>-48.33231232685617</v>
+        <v>-49.24858790790916</v>
       </c>
       <c r="F102">
-        <v>-0.005473932673088102</v>
+        <v>-0.1721122609485845</v>
       </c>
       <c r="G102">
-        <v>-3.607267576078858</v>
+        <v>-1.928920304034544</v>
       </c>
     </row>
   </sheetData>
